--- a/artfynd/A 2209-2023 artfynd.xlsx
+++ b/artfynd/A 2209-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2209-2023 artfynd.xlsx
+++ b/artfynd/A 2209-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,6 +2569,244 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127305563</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58347</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hyllingen, Hyllingenområdet, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>491304</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6411451</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Malmgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Malmgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127305609</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57075</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hyllingen, Hyllingenområdet, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>491304</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6411451</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Malmgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Malmgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
